--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -140,6 +140,192 @@
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>Sales by item</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Q3 Data'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Qty</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Q3 Data'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Widget</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Gadget</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sprocket</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Q3 Data'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Q3 Data'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Q3 Data'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Widget</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Gadget</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sprocket</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Q3 Data'!$C$4:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>9.99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="100001"/>
+        <c:axId val="100002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="100001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="100002"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100001"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R145ee8ed3bff40ba"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,6 +705,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
+  <x:drawing r:id="Rd8b4aabf76734b61"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId5"/>
   </x:tableParts>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -7,9 +7,13 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Q3 Data" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Pivot" sheetId="2" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="0" r:id="rId7"/>
+  </x:pivotCaches>
 </x:workbook>
 </file>
 
@@ -294,7 +298,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -310,7 +314,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvPr id="1" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -319,13 +323,78 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R145ee8ed3bff40ba"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce3d6150786e4bfc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="381000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="SalesPivot" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+  <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
+  <pivotFields count="3">
+    <pivotField name="Item" axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <dataFields count="2">
+    <dataField name="Sum of Qty" fld="1"/>
+    <dataField name="Average of Price" fld="2" subtotal="average"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -624,7 +693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -701,13 +770,140 @@
   <x:mergeCells count="1">
     <x:mergeCell ref="A1:C1"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="B4:B6">
+    <x:cfRule type="dataBar" priority="1">
+      <x:dataBar showValue="1">
+        <x:cfvo type="min" val="0"/>
+        <x:cfvo type="max" val="0"/>
+        <x:color rgb="FF638EC6"/>
+      </x:dataBar>
+      <x:extLst>
+        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}</x14:id>
+        </x:ext>
+      </x:extLst>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C4:C6">
+    <x:cfRule type="colorScale" priority="2">
+      <x:colorScale>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:color rgb="FF63BE7B"/>
+      </x:colorScale>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rd8b4aabf76734b61"/>
+  <x:drawing r:id="R5eafbb0ee0f049d9"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="rId5"/>
+    <x:tablePart r:id="rId8"/>
   </x:tableParts>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF638EC6"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B4:B6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF638EC6"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B4:B6</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </x:ext>
+  </x:extLst>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
+  <x:cacheSource type="worksheet">
+    <x:worksheetSource name="Sales"/>
+  </x:cacheSource>
+  <x:cacheFields>
+    <x:cacheField name="Item">
+      <x:sharedItems count="3">
+        <x:s v="Widget"/>
+        <x:s v="Gadget"/>
+        <x:s v="Sprocket"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Qty">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="40" count="3">
+        <x:n v="12"/>
+        <x:n v="3"/>
+        <x:n v="40"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Price">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.25" maxValue="24.5" count="3">
+        <x:n v="9.99"/>
+        <x:n v="24.5"/>
+        <x:n v="1.25"/>
+      </x:sharedItems>
+    </x:cacheField>
+  </x:cacheFields>
+</x:pivotCacheDefinition>
+</file>
+
+<file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="Widget"/>
+    <n v="12"/>
+    <n v="9.99"/>
+  </r>
+  <r>
+    <s v="Gadget"/>
+    <n v="3"/>
+    <n v="24.5"/>
+  </r>
+  <r>
+    <s v="Sprocket"/>
+    <n v="40"/>
+    <n v="1.25"/>
+  </r>
+</pivotCacheRecords>
 </file>
--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -8,8 +8,13 @@
   <x:sheets>
     <x:sheet name="Q3 Data" sheetId="1" r:id="rId2"/>
     <x:sheet name="Pivot" sheetId="2" r:id="rId5"/>
+    <x:sheet name="Metrics" sheetId="3" r:id="rId12"/>
   </x:sheets>
-  <x:definedNames/>
+  <x:definedNames>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="2">Metrics!$A$1:$F$20</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Metrics!$A$1:$B$5</x:definedName>
+    <x:definedName name="GrowthYs">Metrics!$B$2:$B$5</x:definedName>
+  </x:definedNames>
   <x:calcPr calcId="125725"/>
   <x:pivotCaches>
     <x:pivotCache cacheId="0" r:id="rId7"/>
@@ -42,6 +47,12 @@
   </x:si>
   <x:si>
     <x:t>Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -297,6 +308,119 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>Growth (scatter)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Metrics'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Metrics'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Metrics'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="100001"/>
+        <c:axId val="100002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="100001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="100002"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="100002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100001"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
@@ -323,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce3d6150786e4bfc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re47ffb367e9144eb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -345,7 +469,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12" cstate="print"/>
+        <a:blip r:embed="rId15" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -360,6 +484,41 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree33429a9bb247f3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -779,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}</x14:id>
+          <x14:id>{4B02AC17-E4EE-48FB-8F34-A203530DF83D}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -798,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R5eafbb0ee0f049d9"/>
+  <x:drawing r:id="Rfca3a2fe7ea84307"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -806,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}">
+          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -821,7 +980,22 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{543F8136-AB41-40DD-8BF3-3CCCF1D6BD7B}">
+          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF638EC6"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B4:B6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -853,6 +1027,71 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B7"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>4.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>9.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>16.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:2">
+      <x:c r="B7" s="1">
+        <x:f>SUM(GrowthYs)</x:f>
+        <x:v>32.6</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:B5"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:drawing r:id="R44d6656261a54a98"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re47ffb367e9144eb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9e660f7ad88a47d2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree33429a9bb247f3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R910b7bce02c746ba"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4B02AC17-E4EE-48FB-8F34-A203530DF83D}</x14:id>
+          <x14:id>{6C26F92D-F141-41A4-8F55-DA105CCB74FA}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rfca3a2fe7ea84307"/>
+  <x:drawing r:id="R67fafb3ff3ed49ab"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
+          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
+          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4B02AC17-E4EE-48FB-8F34-A203530DF83D}">
+          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R44d6656261a54a98"/>
+  <x:drawing r:id="Rdac4b2c65e484503"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9e660f7ad88a47d2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f370c0ab8cd404c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R910b7bce02c746ba"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R08173c1eff19425a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6C26F92D-F141-41A4-8F55-DA105CCB74FA}</x14:id>
+          <x14:id>{52EE0064-5664-4240-B3AC-366502E8C02B}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R67fafb3ff3ed49ab"/>
+  <x:drawing r:id="R5f861244a125453b"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
+          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
+          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6C26F92D-F141-41A4-8F55-DA105CCB74FA}">
+          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rdac4b2c65e484503"/>
+  <x:drawing r:id="Rc761ecdd54ac4e0b"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f370c0ab8cd404c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re47717ba808040a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R08173c1eff19425a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5a1e7aca1ad2477e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52EE0064-5664-4240-B3AC-366502E8C02B}</x14:id>
+          <x14:id>{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R5f861244a125453b"/>
+  <x:drawing r:id="R977971294ccc4897"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
+          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
+          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52EE0064-5664-4240-B3AC-366502E8C02B}">
+          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rc761ecdd54ac4e0b"/>
+  <x:drawing r:id="R8808d789f9144662"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re47717ba808040a1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfbcb67ca642d4314"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5a1e7aca1ad2477e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R433005f7c961446a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}</x14:id>
+          <x14:id>{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R977971294ccc4897"/>
+  <x:drawing r:id="Rb0b36d0553274369"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
+          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
+          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BAF980F8-DB24-4F5D-A2B8-66A5DC7CDE1D}">
+          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R8808d789f9144662"/>
+  <x:drawing r:id="Rb000edd7871042d5"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfbcb67ca642d4314"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70e62d2079124445"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R433005f7c961446a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc7d71d8173e4f24"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}</x14:id>
+          <x14:id>{F2628C2C-B876-404A-B031-1FE30C38935F}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rb0b36d0553274369"/>
+  <x:drawing r:id="R9bda98974e834a8e"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
+          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
+          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18588BE6-DAE9-4247-BD0F-8D40BFFA1708}">
+          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rb000edd7871042d5"/>
+  <x:drawing r:id="R291d1f7c21764783"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70e62d2079124445"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09837a73b269483b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc7d71d8173e4f24"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98a0dd179a674bf3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F2628C2C-B876-404A-B031-1FE30C38935F}</x14:id>
+          <x14:id>{403D446D-A72C-404D-9BF0-4F6E11667F5D}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R9bda98974e834a8e"/>
+  <x:drawing r:id="R209782a1f8374990"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
+          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
+          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F2628C2C-B876-404A-B031-1FE30C38935F}">
+          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R291d1f7c21764783"/>
+  <x:drawing r:id="Raa923b7dafd24b78"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09837a73b269483b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R204c87967c4943cf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98a0dd179a674bf3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8579969857d447b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{403D446D-A72C-404D-9BF0-4F6E11667F5D}</x14:id>
+          <x14:id>{F1050E25-2C8E-47A3-9A90-1804D3F9262B}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R209782a1f8374990"/>
+  <x:drawing r:id="Rb149a39a697b4c87"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
+          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
+          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{403D446D-A72C-404D-9BF0-4F6E11667F5D}">
+          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Raa923b7dafd24b78"/>
+  <x:drawing r:id="Ra81fd338619345f4"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R204c87967c4943cf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5bc9c870aaa14c26"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8579969857d447b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R11c0dc6a8c434674"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F1050E25-2C8E-47A3-9A90-1804D3F9262B}</x14:id>
+          <x14:id>{8AAC930D-D0EA-4F24-B737-E6335DA26F42}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rb149a39a697b4c87"/>
+  <x:drawing r:id="R7386fbae6f204afe"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
+          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
+          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F1050E25-2C8E-47A3-9A90-1804D3F9262B}">
+          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Ra81fd338619345f4"/>
+  <x:drawing r:id="Rae3deb4263a446a4"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5bc9c870aaa14c26"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R826ddf15da9048fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R11c0dc6a8c434674"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0cdf34fc31e3429c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8AAC930D-D0EA-4F24-B737-E6335DA26F42}</x14:id>
+          <x14:id>{4BD16F02-2A1E-409D-8FE6-36323D31807A}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R7386fbae6f204afe"/>
+  <x:drawing r:id="R442d37c5d1804004"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
+          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
+          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8AAC930D-D0EA-4F24-B737-E6335DA26F42}">
+          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rae3deb4263a446a4"/>
+  <x:drawing r:id="R22a0e62bcec6472c"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R826ddf15da9048fc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc55f6ce86fd421e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0cdf34fc31e3429c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4a99a52c6504e79"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4BD16F02-2A1E-409D-8FE6-36323D31807A}</x14:id>
+          <x14:id>{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R442d37c5d1804004"/>
+  <x:drawing r:id="R263fba17b363448d"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
+          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
+          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4BD16F02-2A1E-409D-8FE6-36323D31807A}">
+          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R22a0e62bcec6472c"/>
+  <x:drawing r:id="Rd20301598c3c4829"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc55f6ce86fd421e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98f73a363367490f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4a99a52c6504e79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61e55f6b1b7243cd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}</x14:id>
+          <x14:id>{D3A19DF4-81A2-42A2-AF75-612885D4FC22}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R263fba17b363448d"/>
+  <x:drawing r:id="R69daa0ccc8b84f1f"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
+          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
+          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ABCE15C1-EA57-4BDC-8996-19CD5E56D4F8}">
+          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rd20301598c3c4829"/>
+  <x:drawing r:id="Rda70da4ae5fa45b5"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98f73a363367490f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf9ecb7e48a90499e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61e55f6b1b7243cd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ce6d79b1582481e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3A19DF4-81A2-42A2-AF75-612885D4FC22}</x14:id>
+          <x14:id>{15385C58-AA2E-4974-8AD0-E0471855378F}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R69daa0ccc8b84f1f"/>
+  <x:drawing r:id="R9009835098ee4dfb"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
+          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
+          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3A19DF4-81A2-42A2-AF75-612885D4FC22}">
+          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rda70da4ae5fa45b5"/>
+  <x:drawing r:id="Rc3fb87efa1df4d3f"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf9ecb7e48a90499e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24d94db7965449c3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ce6d79b1582481e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf611e905d7ed4c3c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15385C58-AA2E-4974-8AD0-E0471855378F}</x14:id>
+          <x14:id>{C8EE912A-9959-459D-9415-D8BB3B013070}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R9009835098ee4dfb"/>
+  <x:drawing r:id="R25229a38e35741a3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
+          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
+          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15385C58-AA2E-4974-8AD0-E0471855378F}">
+          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Rc3fb87efa1df4d3f"/>
+  <x:drawing r:id="R98a58019fdcd4d9b"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24d94db7965449c3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd3aed8db9fe443b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf611e905d7ed4c3c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19f55c2dbc0d4e02"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C8EE912A-9959-459D-9415-D8BB3B013070}</x14:id>
+          <x14:id>{824A1CD1-167E-43DD-BD53-C5E6EADAC783}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R25229a38e35741a3"/>
+  <x:drawing r:id="R0ac3e2aadbb841e7"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
+          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
+          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C8EE912A-9959-459D-9415-D8BB3B013070}">
+          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R98a58019fdcd4d9b"/>
+  <x:drawing r:id="Ra4c64f63ba0f4e44"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd3aed8db9fe443b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25b999bb23354ceb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19f55c2dbc0d4e02"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bab665dc8b9459c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{824A1CD1-167E-43DD-BD53-C5E6EADAC783}</x14:id>
+          <x14:id>{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R0ac3e2aadbb841e7"/>
+  <x:drawing r:id="R4b761855cda44eca"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
+          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
+          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{824A1CD1-167E-43DD-BD53-C5E6EADAC783}">
+          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="Ra4c64f63ba0f4e44"/>
+  <x:drawing r:id="R2d019ef3a6154c96"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/fixtures/manual-check/excel-sample.xlsx
+++ b/fixtures/manual-check/excel-sample.xlsx
@@ -447,7 +447,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25b999bb23354ceb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99767dd6ed74448d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -513,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bab665dc8b9459c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad57435c41f64847"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,7 +938,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}</x14:id>
+          <x14:id>{F730418D-813F-4A46-830D-51D730FE6886}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -957,7 +957,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R4b761855cda44eca"/>
+  <x:drawing r:id="R9fb70f83b45f41c2"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -965,7 +965,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
+          <x14:cfRule type="dataBar" id="{F730418D-813F-4A46-830D-51D730FE6886}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -980,7 +980,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
+          <x14:cfRule type="dataBar" id="{F730418D-813F-4A46-830D-51D730FE6886}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -995,7 +995,7 @@
           <xm:sqref>B4:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1DE5FE26-86F2-47AA-B938-8F74CFDA658B}">
+          <x14:cfRule type="dataBar" id="{F730418D-813F-4A46-830D-51D730FE6886}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1091,7 +1091,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:drawing r:id="R2d019ef3a6154c96"/>
+  <x:drawing r:id="R102527fde171487c"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
